--- a/public/templates/capa_template.xlsx
+++ b/public/templates/capa_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reycarl-Laptop\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\project_trace_v2\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{803A11FE-4621-4074-AB29-6AC207F81CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC878837-29D4-4173-A80D-4469AAA4CFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AB207AB1-E91A-4BAD-9E4C-0E375EAF874D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Activity</t>
   </si>
@@ -57,7 +57,39 @@
   </si>
   <si>
     <r>
-      <t>Date</t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date To</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(e.g., 08/16/2026)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date From</t>
     </r>
     <r>
       <rPr>
@@ -130,7 +162,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,46 +497,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A60529-953F-456F-A164-CE315E5ACDAA}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576" xr:uid="{26DCA51C-1D3D-4C74-B097-95B25B251003}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1048576 B1:B1048576" xr:uid="{671818B7-5CBD-4CA3-BFA5-82F76025CDE3}">
       <formula1>1</formula1>
-      <formula2>2958465</formula2>
+      <formula2>2958101</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
